--- a/academias/Recursos socioemocionales - Estadisticos 20241.xlsx
+++ b/academias/Recursos socioemocionales - Estadisticos 20241.xlsx
@@ -1469,25 +1469,25 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1504,25 +1504,25 @@
         <v>48</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="J3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1539,25 +1539,25 @@
         <v>36</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1574,25 +1574,25 @@
         <v>37</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1609,25 +1609,25 @@
         <v>33</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1749,25 +1749,25 @@
         <v>23</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1784,25 +1784,25 @@
         <v>19</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1816,25 +1816,25 @@
         <v>344</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="F12">
-        <v>344</v>
+        <v>107</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>31.1</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
-        <v>344</v>
+        <v>107</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1851,25 +1851,25 @@
         <v>40</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1886,25 +1886,25 @@
         <v>24</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1921,25 +1921,25 @@
         <v>36</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1956,25 +1956,25 @@
         <v>28</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1991,25 +1991,25 @@
         <v>35</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2026,25 +2026,25 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2061,25 +2061,25 @@
         <v>37</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="F19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2096,25 +2096,25 @@
         <v>21</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2131,25 +2131,25 @@
         <v>25</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2166,25 +2166,25 @@
         <v>19</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2201,25 +2201,25 @@
         <v>21</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2236,25 +2236,25 @@
         <v>10</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G24" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2268,25 +2268,25 @@
         <v>320</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="F25">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="G25" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="K25" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -2297,25 +2297,25 @@
         <v>664</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="F26">
-        <v>664</v>
+        <v>107</v>
       </c>
       <c r="G26" s="1">
-        <v>0</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="H26" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
       <c r="I26" s="2">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="J26">
-        <v>664</v>
+        <v>107</v>
       </c>
       <c r="K26" s="1">
-        <v>100</v>
+        <v>16.1</v>
       </c>
     </row>
   </sheetData>
@@ -2383,19 +2383,19 @@
         <v>41</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
-        <v>100</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H2" s="1">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="I2" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -2418,19 +2418,19 @@
         <v>48</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="I3" s="2">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -2730,19 +2730,19 @@
         <v>344</v>
       </c>
       <c r="E12">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I12" s="2">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2765,19 +2765,19 @@
         <v>40</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F13">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>97.5</v>
+        <v>85</v>
       </c>
       <c r="H13" s="1">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="I13" s="2">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -3182,16 +3182,16 @@
         <v>320</v>
       </c>
       <c r="E25">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F25">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G25" s="1">
-        <v>12.2</v>
+        <v>10.6</v>
       </c>
       <c r="H25" s="1">
-        <v>87.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I25" s="2">
         <v>0.8</v>
@@ -3211,19 +3211,19 @@
         <v>664</v>
       </c>
       <c r="E26">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="F26">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="G26" s="1">
-        <v>57.7</v>
+        <v>55.3</v>
       </c>
       <c r="H26" s="1">
-        <v>42.3</v>
+        <v>44.7</v>
       </c>
       <c r="I26" s="2">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J26">
         <v>280</v>

--- a/academias/Recursos socioemocionales - Estadisticos 20241.xlsx
+++ b/academias/Recursos socioemocionales - Estadisticos 20241.xlsx
@@ -1644,25 +1644,25 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="J7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1679,25 +1679,25 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="F8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1714,25 +1714,25 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1816,25 +1816,25 @@
         <v>344</v>
       </c>
       <c r="E12">
-        <v>237</v>
+        <v>344</v>
       </c>
       <c r="F12">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>68.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>31.1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>9.5</v>
       </c>
       <c r="J12">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>31.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2297,25 +2297,25 @@
         <v>664</v>
       </c>
       <c r="E26">
-        <v>557</v>
+        <v>664</v>
       </c>
       <c r="F26">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="G26" s="1">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H26" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="2">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K26" s="1">
-        <v>16.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2558,19 +2558,19 @@
         <v>40</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -2593,19 +2593,19 @@
         <v>34</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
-        <v>100</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="I8" s="2">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2628,19 +2628,19 @@
         <v>33</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>75.8</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="I9" s="2">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -2730,19 +2730,19 @@
         <v>344</v>
       </c>
       <c r="E12">
-        <v>333</v>
+        <v>309</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1">
-        <v>96.8</v>
+        <v>89.8</v>
       </c>
       <c r="H12" s="1">
-        <v>3.2</v>
+        <v>10.2</v>
       </c>
       <c r="I12" s="2">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -3211,19 +3211,19 @@
         <v>664</v>
       </c>
       <c r="E26">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="F26">
-        <v>297</v>
+        <v>321</v>
       </c>
       <c r="G26" s="1">
-        <v>55.3</v>
+        <v>51.7</v>
       </c>
       <c r="H26" s="1">
-        <v>44.7</v>
+        <v>48.3</v>
       </c>
       <c r="I26" s="2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J26">
         <v>280</v>

--- a/academias/Recursos socioemocionales - Estadisticos 20241.xlsx
+++ b/academias/Recursos socioemocionales - Estadisticos 20241.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="38">
   <si>
     <t>Docente</t>
   </si>
@@ -51,24 +51,24 @@
     <t>por_blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Recursos socioemocionales III</t>
+  </si>
+  <si>
     <t>Totales Docente</t>
   </si>
   <si>
-    <t>Recursos socioemocionales III</t>
-  </si>
-  <si>
     <t>Totales Generales</t>
   </si>
   <si>
+    <t>1AM</t>
+  </si>
+  <si>
     <t>1BM</t>
   </si>
   <si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t>1EV</t>
-  </si>
-  <si>
-    <t>1AM</t>
   </si>
   <si>
     <t>3AEM</t>
@@ -496,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -546,33 +543,24 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" s="1">
-        <v>100</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
       <c r="I2" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -581,33 +569,24 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" s="1">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
       <c r="I3" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -616,33 +595,24 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" s="1">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
       <c r="I4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -651,33 +621,24 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" s="1">
-        <v>100</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
       <c r="I5" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -686,33 +647,24 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" s="1">
-        <v>100</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -721,33 +673,24 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" s="1">
-        <v>100</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
       <c r="I7" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -756,33 +699,24 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
-        <v>100</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
       <c r="I8" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -791,33 +725,24 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9" s="1">
-        <v>100</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
       <c r="I9" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -826,33 +751,24 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10" s="1">
-        <v>100</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -861,33 +777,24 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="1">
-        <v>100</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
       <c r="I11" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -896,36 +803,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12" s="1">
-        <v>100</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
       <c r="I12" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -934,473 +835,321 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1">
-        <v>97.5</v>
-      </c>
-      <c r="H13" s="1">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="1">
-        <v>100</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
       <c r="I14" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
       <c r="D15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="G15" s="1">
-        <v>100</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
       <c r="I15" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="G16" s="1">
-        <v>100</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
       <c r="D17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
-      <c r="G17" s="1">
-        <v>100</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
       <c r="I17" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
       </c>
       <c r="D18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18" s="1">
-        <v>100</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
       <c r="I18" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>2</v>
-      </c>
-      <c r="G19" s="1">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="H19" s="1">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
       </c>
       <c r="D20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" s="1">
-        <v>100</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" s="1">
-        <v>100</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
       <c r="I21" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22" s="1">
-        <v>100</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
       <c r="I22" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" s="1">
-        <v>100</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
       <c r="I23" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-      <c r="E24">
-        <v>10</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>100</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>10</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
       <c r="D25">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>317</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>3</v>
-      </c>
-      <c r="G25" s="1">
-        <v>99.09999999999999</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26">
-        <v>664</v>
-      </c>
-      <c r="E26">
-        <v>661</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26" s="1">
-        <v>99.5</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="I26" s="2">
-        <v>10</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1411,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -1460,33 +1209,24 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" s="1">
-        <v>100</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1495,33 +1235,24 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" s="1">
-        <v>100</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
       <c r="I3" s="2">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1530,33 +1261,24 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" s="1">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
       <c r="I4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1565,33 +1287,24 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" s="1">
-        <v>100</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
       <c r="I5" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1600,33 +1313,24 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" s="1">
-        <v>100</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1635,33 +1339,24 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" s="1">
-        <v>100</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1670,33 +1365,24 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
-      <c r="G8" s="1">
-        <v>100</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1705,33 +1391,24 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
       </c>
-      <c r="G9" s="1">
-        <v>100</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
       <c r="I9" s="2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1740,33 +1417,24 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10" s="1">
-        <v>100</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1775,33 +1443,24 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="1">
-        <v>100</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
       <c r="I11" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1810,36 +1469,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12" s="1">
-        <v>100</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0</v>
-      </c>
       <c r="I12" s="2">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1848,473 +1501,321 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
-      <c r="G13" s="1">
-        <v>100</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
       <c r="I13" s="2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
-      <c r="G14" s="1">
-        <v>100</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
       <c r="I14" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
       <c r="D15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>0</v>
       </c>
-      <c r="G15" s="1">
-        <v>100</v>
-      </c>
-      <c r="H15" s="1">
-        <v>0</v>
-      </c>
       <c r="I15" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>0</v>
       </c>
-      <c r="G16" s="1">
-        <v>100</v>
-      </c>
-      <c r="H16" s="1">
-        <v>0</v>
-      </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
       <c r="D17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>0</v>
       </c>
-      <c r="G17" s="1">
-        <v>100</v>
-      </c>
-      <c r="H17" s="1">
-        <v>0</v>
-      </c>
       <c r="I17" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
-      <c r="K17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
       </c>
       <c r="D18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
-      <c r="G18" s="1">
-        <v>100</v>
-      </c>
-      <c r="H18" s="1">
-        <v>0</v>
-      </c>
       <c r="I18" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>0</v>
       </c>
-      <c r="G19" s="1">
-        <v>100</v>
-      </c>
-      <c r="H19" s="1">
-        <v>0</v>
-      </c>
       <c r="I19" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
       </c>
       <c r="D20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
-      <c r="G20" s="1">
-        <v>100</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
       <c r="I20" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
-      <c r="K20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
-      <c r="G21" s="1">
-        <v>100</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
       <c r="I21" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
       </c>
-      <c r="K21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>0</v>
       </c>
-      <c r="G22" s="1">
-        <v>100</v>
-      </c>
-      <c r="H22" s="1">
-        <v>0</v>
-      </c>
       <c r="I22" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
-      <c r="K22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>0</v>
       </c>
-      <c r="G23" s="1">
-        <v>100</v>
-      </c>
-      <c r="H23" s="1">
-        <v>0</v>
-      </c>
       <c r="I23" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-      <c r="E24">
-        <v>10</v>
-      </c>
-      <c r="F24">
-        <v>0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>100</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="2">
-        <v>10</v>
-      </c>
-      <c r="J24">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
       <c r="D25">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
-      <c r="G25" s="1">
-        <v>100</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
       <c r="I25" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26">
-        <v>664</v>
-      </c>
-      <c r="E26">
-        <v>664</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1">
-        <v>100</v>
-      </c>
-      <c r="H26" s="1">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2325,7 +1826,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="30.7109375" customWidth="1"/>
@@ -2374,33 +1875,24 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="H2" s="1">
-        <v>24.4</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2409,33 +1901,24 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D3">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>97.90000000000001</v>
-      </c>
-      <c r="H3" s="1">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2444,33 +1927,24 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" s="1">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
       <c r="I4" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2479,33 +1953,24 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="G5" s="1">
-        <v>100</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
-      </c>
       <c r="I5" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2514,33 +1979,24 @@
         <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="G6" s="1">
-        <v>100</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
       <c r="I6" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2549,33 +2005,24 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7" s="1">
-        <v>87.5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2584,33 +2031,24 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>11</v>
-      </c>
-      <c r="G8" s="1">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="H8" s="1">
-        <v>32.4</v>
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2619,33 +2057,24 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9" s="1">
-        <v>75.8</v>
-      </c>
-      <c r="H9" s="1">
-        <v>24.2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2654,33 +2083,24 @@
         <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="G10" s="1">
-        <v>100</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
       <c r="I10" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2689,33 +2109,24 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="G11" s="1">
-        <v>100</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
       <c r="I11" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
         <v>0</v>
       </c>
     </row>
@@ -2724,36 +2135,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
       </c>
       <c r="D12">
-        <v>344</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>309</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>35</v>
-      </c>
-      <c r="G12" s="1">
-        <v>89.8</v>
-      </c>
-      <c r="H12" s="1">
-        <v>10.2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -2762,474 +2167,322 @@
         <v>27</v>
       </c>
       <c r="D13">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>6</v>
-      </c>
-      <c r="G13" s="1">
-        <v>85</v>
-      </c>
-      <c r="H13" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>24</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
-      </c>
-      <c r="H14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
       </c>
       <c r="J14">
-        <v>24</v>
-      </c>
-      <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
         <v>29</v>
       </c>
       <c r="D15">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>36</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
-      </c>
-      <c r="H15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>36</v>
-      </c>
-      <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C16" t="s">
         <v>30</v>
       </c>
       <c r="D16">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="F16">
-        <v>28</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>28</v>
-      </c>
-      <c r="K16" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
       </c>
       <c r="D17">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E17">
         <v>0</v>
       </c>
       <c r="F17">
-        <v>35</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
         <v>0</v>
       </c>
       <c r="J17">
-        <v>35</v>
-      </c>
-      <c r="K17" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="s">
         <v>32</v>
       </c>
       <c r="D18">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E18">
         <v>0</v>
       </c>
       <c r="F18">
-        <v>24</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
-      </c>
-      <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
         <v>0</v>
       </c>
       <c r="J18">
-        <v>24</v>
-      </c>
-      <c r="K18" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
       </c>
       <c r="D19">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>37</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="2">
         <v>0</v>
       </c>
       <c r="J19">
-        <v>37</v>
-      </c>
-      <c r="K19" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
         <v>34</v>
       </c>
       <c r="D20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>21</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="2">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>21</v>
-      </c>
-      <c r="K20" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C21" t="s">
         <v>35</v>
       </c>
       <c r="D21">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>25</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>25</v>
-      </c>
-      <c r="K21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C22" t="s">
         <v>36</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22">
-        <v>19</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
-      </c>
-      <c r="H22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="2">
         <v>0</v>
       </c>
       <c r="J22">
-        <v>19</v>
-      </c>
-      <c r="K22" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
       </c>
       <c r="D23">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>21</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="2">
         <v>0</v>
       </c>
       <c r="J23">
-        <v>21</v>
-      </c>
-      <c r="K23" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="B25" t="s">
         <v>15</v>
       </c>
-      <c r="C24" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24">
-        <v>10</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>100</v>
-      </c>
-      <c r="I24" s="2">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>10</v>
-      </c>
-      <c r="K24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>14</v>
-      </c>
       <c r="D25">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>286</v>
-      </c>
-      <c r="G25" s="1">
-        <v>10.6</v>
-      </c>
-      <c r="H25" s="1">
-        <v>89.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="I25" s="2">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>280</v>
-      </c>
-      <c r="K25" s="1">
-        <v>87.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="D26">
-        <v>664</v>
-      </c>
-      <c r="E26">
-        <v>343</v>
-      </c>
-      <c r="F26">
-        <v>321</v>
-      </c>
-      <c r="G26" s="1">
-        <v>51.7</v>
-      </c>
-      <c r="H26" s="1">
-        <v>48.3</v>
-      </c>
-      <c r="I26" s="2">
-        <v>4.8</v>
-      </c>
-      <c r="J26">
-        <v>280</v>
-      </c>
-      <c r="K26" s="1">
-        <v>42.2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
